--- a/data/meat_data.xlsx
+++ b/data/meat_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:F366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,11 +459,6 @@
           <t>Table_Count</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Source_File</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -486,11 +481,6 @@
       <c r="F2" t="n">
         <v>62</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -513,11 +503,6 @@
       <c r="F3" t="n">
         <v>40</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -540,11 +525,6 @@
       <c r="F4" t="n">
         <v>38</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,11 +547,6 @@
       <c r="F5" t="n">
         <v>59</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -594,11 +569,6 @@
       <c r="F6" t="n">
         <v>44</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -621,11 +591,6 @@
       <c r="F7" t="n">
         <v>58</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,11 +613,6 @@
       <c r="F8" t="n">
         <v>61</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -675,11 +635,6 @@
       <c r="F9" t="n">
         <v>56</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -702,11 +657,6 @@
       <c r="F10" t="n">
         <v>50</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -729,11 +679,6 @@
       <c r="F11" t="n">
         <v>52</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -756,11 +701,6 @@
       <c r="F12" t="n">
         <v>60</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -783,11 +723,6 @@
       <c r="F13" t="n">
         <v>37</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -810,11 +745,6 @@
       <c r="F14" t="n">
         <v>50</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,11 +767,6 @@
       <c r="F15" t="n">
         <v>67</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -864,11 +789,6 @@
       <c r="F16" t="n">
         <v>61</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -891,11 +811,6 @@
       <c r="F17" t="n">
         <v>57</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -918,11 +833,6 @@
       <c r="F18" t="n">
         <v>47</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -945,11 +855,6 @@
       <c r="F19" t="n">
         <v>48</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -972,11 +877,6 @@
       <c r="F20" t="n">
         <v>54</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -999,11 +899,6 @@
       <c r="F21" t="n">
         <v>54</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1026,11 +921,6 @@
       <c r="F22" t="n">
         <v>65</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1053,11 +943,6 @@
       <c r="F23" t="n">
         <v>38</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1080,11 +965,6 @@
       <c r="F24" t="n">
         <v>61</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1107,11 +987,6 @@
       <c r="F25" t="n">
         <v>56</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1134,11 +1009,6 @@
       <c r="F26" t="n">
         <v>64</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1161,11 +1031,6 @@
       <c r="F27" t="n">
         <v>60</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1188,11 +1053,6 @@
       <c r="F28" t="n">
         <v>58</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1215,11 +1075,6 @@
       <c r="F29" t="n">
         <v>56</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>202502.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1242,11 +1097,6 @@
       <c r="F30" t="n">
         <v>104</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1269,11 +1119,6 @@
       <c r="F31" t="n">
         <v>62</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1296,11 +1141,6 @@
       <c r="F32" t="n">
         <v>35</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1323,11 +1163,6 @@
       <c r="F33" t="n">
         <v>38</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1350,11 +1185,6 @@
       <c r="F34" t="n">
         <v>56</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1377,11 +1207,6 @@
       <c r="F35" t="n">
         <v>58</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1404,11 +1229,6 @@
       <c r="F36" t="n">
         <v>68</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1431,11 +1251,6 @@
       <c r="F37" t="n">
         <v>60</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1458,11 +1273,6 @@
       <c r="F38" t="n">
         <v>57</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1485,11 +1295,6 @@
       <c r="F39" t="n">
         <v>53</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1512,11 +1317,6 @@
       <c r="F40" t="n">
         <v>74</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1539,11 +1339,6 @@
       <c r="F41" t="n">
         <v>70</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1566,11 +1361,6 @@
       <c r="F42" t="n">
         <v>85</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1593,11 +1383,6 @@
       <c r="F43" t="n">
         <v>75</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1620,11 +1405,6 @@
       <c r="F44" t="n">
         <v>75</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1647,11 +1427,6 @@
       <c r="F45" t="n">
         <v>67</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1674,11 +1449,6 @@
       <c r="F46" t="n">
         <v>60</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1701,11 +1471,6 @@
       <c r="F47" t="n">
         <v>43</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1728,11 +1493,6 @@
       <c r="F48" t="n">
         <v>43</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1755,11 +1515,6 @@
       <c r="F49" t="n">
         <v>65</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1782,11 +1537,6 @@
       <c r="F50" t="n">
         <v>82</v>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1809,11 +1559,6 @@
       <c r="F51" t="n">
         <v>77</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1836,11 +1581,6 @@
       <c r="F52" t="n">
         <v>73</v>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1863,11 +1603,6 @@
       <c r="F53" t="n">
         <v>53</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1890,11 +1625,6 @@
       <c r="F54" t="n">
         <v>53</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1917,11 +1647,6 @@
       <c r="F55" t="n">
         <v>62</v>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1944,11 +1669,6 @@
       <c r="F56" t="n">
         <v>75</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1971,11 +1691,6 @@
       <c r="F57" t="n">
         <v>79</v>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1998,11 +1713,6 @@
       <c r="F58" t="n">
         <v>72</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2025,11 +1735,6 @@
       <c r="F59" t="n">
         <v>71</v>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2052,11 +1757,6 @@
       <c r="F60" t="n">
         <v>54</v>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>202503.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2079,11 +1779,6 @@
       <c r="F61" t="n">
         <v>74</v>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2106,11 +1801,6 @@
       <c r="F62" t="n">
         <v>70</v>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2133,11 +1823,6 @@
       <c r="F63" t="n">
         <v>67</v>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2160,11 +1845,6 @@
       <c r="F64" t="n">
         <v>72</v>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2187,11 +1867,6 @@
       <c r="F65" t="n">
         <v>63</v>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2214,11 +1889,6 @@
       <c r="F66" t="n">
         <v>61</v>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2241,11 +1911,6 @@
       <c r="F67" t="n">
         <v>60</v>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2268,11 +1933,6 @@
       <c r="F68" t="n">
         <v>58</v>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2295,11 +1955,6 @@
       <c r="F69" t="n">
         <v>78</v>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2322,11 +1977,6 @@
       <c r="F70" t="n">
         <v>78</v>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2349,11 +1999,6 @@
       <c r="F71" t="n">
         <v>67</v>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2376,11 +2021,6 @@
       <c r="F72" t="n">
         <v>48</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2403,11 +2043,6 @@
       <c r="F73" t="n">
         <v>58</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2430,11 +2065,6 @@
       <c r="F74" t="n">
         <v>44</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2457,11 +2087,6 @@
       <c r="F75" t="n">
         <v>69</v>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2484,11 +2109,6 @@
       <c r="F76" t="n">
         <v>62</v>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2511,11 +2131,6 @@
       <c r="F77" t="n">
         <v>54</v>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2538,11 +2153,6 @@
       <c r="F78" t="n">
         <v>79</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2565,11 +2175,6 @@
       <c r="F79" t="n">
         <v>62</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2592,11 +2197,6 @@
       <c r="F80" t="n">
         <v>66</v>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2619,11 +2219,6 @@
       <c r="F81" t="n">
         <v>59</v>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2646,11 +2241,6 @@
       <c r="F82" t="n">
         <v>60</v>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2673,11 +2263,6 @@
       <c r="F83" t="n">
         <v>78</v>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2700,11 +2285,6 @@
       <c r="F84" t="n">
         <v>64</v>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2727,11 +2307,6 @@
       <c r="F85" t="n">
         <v>65</v>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2754,11 +2329,6 @@
       <c r="F86" t="n">
         <v>66</v>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2781,11 +2351,6 @@
       <c r="F87" t="n">
         <v>64</v>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2808,11 +2373,6 @@
       <c r="F88" t="n">
         <v>61</v>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2835,11 +2395,6 @@
       <c r="F89" t="n">
         <v>52</v>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2862,11 +2417,6 @@
       <c r="F90" t="n">
         <v>70</v>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>202504.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2889,11 +2439,6 @@
       <c r="F91" t="n">
         <v>80</v>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2916,11 +2461,6 @@
       <c r="F92" t="n">
         <v>70</v>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2943,11 +2483,6 @@
       <c r="F93" t="n">
         <v>64</v>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2970,11 +2505,6 @@
       <c r="F94" t="n">
         <v>82</v>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2997,11 +2527,6 @@
       <c r="F95" t="n">
         <v>69</v>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3024,11 +2549,6 @@
       <c r="F96" t="n">
         <v>50</v>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3051,11 +2571,6 @@
       <c r="F97" t="n">
         <v>47</v>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3078,11 +2593,6 @@
       <c r="F98" t="n">
         <v>67</v>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3105,11 +2615,6 @@
       <c r="F99" t="n">
         <v>56</v>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3132,11 +2637,6 @@
       <c r="F100" t="n">
         <v>54</v>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3159,11 +2659,6 @@
       <c r="F101" t="n">
         <v>60</v>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3186,11 +2681,6 @@
       <c r="F102" t="n">
         <v>60</v>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3213,11 +2703,6 @@
       <c r="F103" t="n">
         <v>73</v>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3240,11 +2725,6 @@
       <c r="F104" t="n">
         <v>54</v>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3267,11 +2747,6 @@
       <c r="F105" t="n">
         <v>51</v>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3294,11 +2769,6 @@
       <c r="F106" t="n">
         <v>48</v>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3321,11 +2791,6 @@
       <c r="F107" t="n">
         <v>64</v>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3348,11 +2813,6 @@
       <c r="F108" t="n">
         <v>74</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3375,11 +2835,6 @@
       <c r="F109" t="n">
         <v>63</v>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3402,11 +2857,6 @@
       <c r="F110" t="n">
         <v>52</v>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3429,11 +2879,6 @@
       <c r="F111" t="n">
         <v>72</v>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3456,11 +2901,6 @@
       <c r="F112" t="n">
         <v>78</v>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3483,11 +2923,6 @@
       <c r="F113" t="n">
         <v>78</v>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3510,11 +2945,6 @@
       <c r="F114" t="n">
         <v>61</v>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3537,11 +2967,6 @@
       <c r="F115" t="n">
         <v>59</v>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3564,11 +2989,6 @@
       <c r="F116" t="n">
         <v>66</v>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3591,11 +3011,6 @@
       <c r="F117" t="n">
         <v>56</v>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3618,11 +3033,6 @@
       <c r="F118" t="n">
         <v>66</v>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3645,11 +3055,6 @@
       <c r="F119" t="n">
         <v>65</v>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3672,11 +3077,6 @@
       <c r="F120" t="n">
         <v>73</v>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3699,11 +3099,6 @@
       <c r="F121" t="n">
         <v>49</v>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>202505.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3726,11 +3121,6 @@
       <c r="F122" t="n">
         <v>52</v>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3753,11 +3143,6 @@
       <c r="F123" t="n">
         <v>68</v>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3780,11 +3165,6 @@
       <c r="F124" t="n">
         <v>44</v>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3807,11 +3187,6 @@
       <c r="F125" t="n">
         <v>61</v>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3834,11 +3209,6 @@
       <c r="F126" t="n">
         <v>61</v>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3861,11 +3231,6 @@
       <c r="F127" t="n">
         <v>43</v>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3888,11 +3253,6 @@
       <c r="F128" t="n">
         <v>55</v>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3915,11 +3275,6 @@
       <c r="F129" t="n">
         <v>40</v>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3942,11 +3297,6 @@
       <c r="F130" t="n">
         <v>69</v>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3969,11 +3319,6 @@
       <c r="F131" t="n">
         <v>54</v>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3996,11 +3341,6 @@
       <c r="F132" t="n">
         <v>63</v>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4023,11 +3363,6 @@
       <c r="F133" t="n">
         <v>63</v>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4050,11 +3385,6 @@
       <c r="F134" t="n">
         <v>60</v>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4077,11 +3407,6 @@
       <c r="F135" t="n">
         <v>61</v>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4104,11 +3429,6 @@
       <c r="F136" t="n">
         <v>69</v>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4131,11 +3451,6 @@
       <c r="F137" t="n">
         <v>0</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4158,11 +3473,6 @@
       <c r="F138" t="n">
         <v>63</v>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4185,11 +3495,6 @@
       <c r="F139" t="n">
         <v>77</v>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4212,11 +3517,6 @@
       <c r="F140" t="n">
         <v>66</v>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4239,11 +3539,6 @@
       <c r="F141" t="n">
         <v>56</v>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4266,11 +3561,6 @@
       <c r="F142" t="n">
         <v>71</v>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4293,11 +3583,6 @@
       <c r="F143" t="n">
         <v>50</v>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4320,11 +3605,6 @@
       <c r="F144" t="n">
         <v>67</v>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4347,11 +3627,6 @@
       <c r="F145" t="n">
         <v>63</v>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4374,11 +3649,6 @@
       <c r="F146" t="n">
         <v>81</v>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4401,11 +3671,6 @@
       <c r="F147" t="n">
         <v>72</v>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4428,11 +3693,6 @@
       <c r="F148" t="n">
         <v>82</v>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4455,11 +3715,6 @@
       <c r="F149" t="n">
         <v>70</v>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4482,11 +3737,6 @@
       <c r="F150" t="n">
         <v>71</v>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4509,11 +3759,6 @@
       <c r="F151" t="n">
         <v>57</v>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>202506.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4536,11 +3781,6 @@
       <c r="F152" t="n">
         <v>60</v>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4563,11 +3803,6 @@
       <c r="F153" t="n">
         <v>73</v>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4590,11 +3825,6 @@
       <c r="F154" t="n">
         <v>61</v>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4617,11 +3847,6 @@
       <c r="F155" t="n">
         <v>0</v>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4644,11 +3869,6 @@
       <c r="F156" t="n">
         <v>57</v>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4671,11 +3891,6 @@
       <c r="F157" t="n">
         <v>71</v>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4698,11 +3913,6 @@
       <c r="F158" t="n">
         <v>67</v>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4725,11 +3935,6 @@
       <c r="F159" t="n">
         <v>53</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4752,11 +3957,6 @@
       <c r="F160" t="n">
         <v>56</v>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4779,11 +3979,6 @@
       <c r="F161" t="n">
         <v>63</v>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4806,11 +4001,6 @@
       <c r="F162" t="n">
         <v>69</v>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4833,11 +4023,6 @@
       <c r="F163" t="n">
         <v>54</v>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4860,11 +4045,6 @@
       <c r="F164" t="n">
         <v>50</v>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4887,11 +4067,6 @@
       <c r="F165" t="n">
         <v>62</v>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4914,11 +4089,6 @@
       <c r="F166" t="n">
         <v>44</v>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4941,11 +4111,6 @@
       <c r="F167" t="n">
         <v>37</v>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4968,11 +4133,6 @@
       <c r="F168" t="n">
         <v>56</v>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4995,11 +4155,6 @@
       <c r="F169" t="n">
         <v>58</v>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5022,11 +4177,6 @@
       <c r="F170" t="n">
         <v>52</v>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5049,11 +4199,6 @@
       <c r="F171" t="n">
         <v>63</v>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5076,11 +4221,6 @@
       <c r="F172" t="n">
         <v>58</v>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5103,11 +4243,6 @@
       <c r="F173" t="n">
         <v>49</v>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5130,11 +4265,6 @@
       <c r="F174" t="n">
         <v>46</v>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5157,11 +4287,6 @@
       <c r="F175" t="n">
         <v>57</v>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5184,11 +4309,6 @@
       <c r="F176" t="n">
         <v>66</v>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5211,11 +4331,6 @@
       <c r="F177" t="n">
         <v>59</v>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5238,11 +4353,6 @@
       <c r="F178" t="n">
         <v>63</v>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5265,11 +4375,6 @@
       <c r="F179" t="n">
         <v>55</v>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5292,11 +4397,6 @@
       <c r="F180" t="n">
         <v>0</v>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5319,11 +4419,6 @@
       <c r="F181" t="n">
         <v>54</v>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5346,11 +4441,6 @@
       <c r="F182" t="n">
         <v>67</v>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>202507.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5373,11 +4463,6 @@
       <c r="F183" t="n">
         <v>61</v>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5400,11 +4485,6 @@
       <c r="F184" t="n">
         <v>61</v>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5427,11 +4507,6 @@
       <c r="F185" t="n">
         <v>61</v>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5454,11 +4529,6 @@
       <c r="F186" t="n">
         <v>61</v>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5481,11 +4551,6 @@
       <c r="F187" t="n">
         <v>61</v>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5508,11 +4573,6 @@
       <c r="F188" t="n">
         <v>61</v>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5535,11 +4595,6 @@
       <c r="F189" t="n">
         <v>61</v>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5562,11 +4617,6 @@
       <c r="F190" t="n">
         <v>67</v>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5589,11 +4639,6 @@
       <c r="F191" t="n">
         <v>55</v>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5616,11 +4661,6 @@
       <c r="F192" t="n">
         <v>70</v>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5643,11 +4683,6 @@
       <c r="F193" t="n">
         <v>60</v>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5670,11 +4705,6 @@
       <c r="F194" t="n">
         <v>56</v>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5697,11 +4727,6 @@
       <c r="F195" t="n">
         <v>61</v>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5724,11 +4749,6 @@
       <c r="F196" t="n">
         <v>63</v>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5751,11 +4771,6 @@
       <c r="F197" t="n">
         <v>71</v>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5778,11 +4793,6 @@
       <c r="F198" t="n">
         <v>69</v>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5805,11 +4815,6 @@
       <c r="F199" t="n">
         <v>63</v>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5832,11 +4837,6 @@
       <c r="F200" t="n">
         <v>60</v>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5859,11 +4859,6 @@
       <c r="F201" t="n">
         <v>60</v>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5886,11 +4881,6 @@
       <c r="F202" t="n">
         <v>64</v>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5913,11 +4903,6 @@
       <c r="F203" t="n">
         <v>65</v>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5940,11 +4925,6 @@
       <c r="F204" t="n">
         <v>63</v>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5967,11 +4947,6 @@
       <c r="F205" t="n">
         <v>43</v>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5994,11 +4969,6 @@
       <c r="F206" t="n">
         <v>62</v>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6021,11 +4991,6 @@
       <c r="F207" t="n">
         <v>61</v>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6048,11 +5013,6 @@
       <c r="F208" t="n">
         <v>70</v>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6075,11 +5035,6 @@
       <c r="F209" t="n">
         <v>62</v>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6102,11 +5057,6 @@
       <c r="F210" t="n">
         <v>69</v>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6129,11 +5079,6 @@
       <c r="F211" t="n">
         <v>69</v>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6156,11 +5101,6 @@
       <c r="F212" t="n">
         <v>43</v>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6183,11 +5123,6 @@
       <c r="F213" t="n">
         <v>58</v>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>202508.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6210,11 +5145,6 @@
       <c r="F214" t="n">
         <v>56</v>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6237,11 +5167,6 @@
       <c r="F215" t="n">
         <v>65</v>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6264,11 +5189,6 @@
       <c r="F216" t="n">
         <v>53</v>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6291,11 +5211,6 @@
       <c r="F217" t="n">
         <v>66</v>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6318,11 +5233,6 @@
       <c r="F218" t="n">
         <v>59</v>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6345,11 +5255,6 @@
       <c r="F219" t="n">
         <v>55</v>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6372,11 +5277,6 @@
       <c r="F220" t="n">
         <v>66</v>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6399,11 +5299,6 @@
       <c r="F221" t="n">
         <v>51</v>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6426,11 +5321,6 @@
       <c r="F222" t="n">
         <v>55</v>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6453,11 +5343,6 @@
       <c r="F223" t="n">
         <v>58</v>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6480,11 +5365,6 @@
       <c r="F224" t="n">
         <v>61</v>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6507,11 +5387,6 @@
       <c r="F225" t="n">
         <v>64</v>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6534,11 +5409,6 @@
       <c r="F226" t="n">
         <v>61</v>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6561,11 +5431,6 @@
       <c r="F227" t="n">
         <v>63</v>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6588,11 +5453,6 @@
       <c r="F228" t="n">
         <v>61</v>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6615,11 +5475,6 @@
       <c r="F229" t="n">
         <v>44</v>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6642,11 +5497,6 @@
       <c r="F230" t="n">
         <v>53</v>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6669,11 +5519,6 @@
       <c r="F231" t="n">
         <v>51</v>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6696,11 +5541,6 @@
       <c r="F232" t="n">
         <v>58</v>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6723,11 +5563,6 @@
       <c r="F233" t="n">
         <v>39</v>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6750,11 +5585,6 @@
       <c r="F234" t="n">
         <v>58</v>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6777,11 +5607,6 @@
       <c r="F235" t="n">
         <v>50</v>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6804,11 +5629,6 @@
       <c r="F236" t="n">
         <v>40</v>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6831,11 +5651,6 @@
       <c r="F237" t="n">
         <v>37</v>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6858,11 +5673,6 @@
       <c r="F238" t="n">
         <v>62</v>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6885,11 +5695,6 @@
       <c r="F239" t="n">
         <v>49</v>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6912,11 +5717,6 @@
       <c r="F240" t="n">
         <v>62</v>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6939,11 +5739,6 @@
       <c r="F241" t="n">
         <v>40</v>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6966,11 +5761,6 @@
       <c r="F242" t="n">
         <v>45</v>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6993,11 +5783,6 @@
       <c r="F243" t="n">
         <v>56</v>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>202509.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7020,11 +5805,6 @@
       <c r="F244" t="n">
         <v>40</v>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7047,11 +5827,6 @@
       <c r="F245" t="n">
         <v>74</v>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7074,11 +5849,6 @@
       <c r="F246" t="n">
         <v>43</v>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7101,11 +5871,6 @@
       <c r="F247" t="n">
         <v>63</v>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7128,11 +5893,6 @@
       <c r="F248" t="n">
         <v>69</v>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7155,11 +5915,6 @@
       <c r="F249" t="n">
         <v>90</v>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7182,11 +5937,6 @@
       <c r="F250" t="n">
         <v>59</v>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7209,11 +5959,6 @@
       <c r="F251" t="n">
         <v>55</v>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7236,11 +5981,6 @@
       <c r="F252" t="n">
         <v>64</v>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7263,11 +6003,6 @@
       <c r="F253" t="n">
         <v>62</v>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7290,11 +6025,6 @@
       <c r="F254" t="n">
         <v>59</v>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7317,11 +6047,6 @@
       <c r="F255" t="n">
         <v>47</v>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7344,11 +6069,6 @@
       <c r="F256" t="n">
         <v>50</v>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7371,11 +6091,6 @@
       <c r="F257" t="n">
         <v>51</v>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7398,11 +6113,6 @@
       <c r="F258" t="n">
         <v>53</v>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7425,11 +6135,6 @@
       <c r="F259" t="n">
         <v>74</v>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7452,11 +6157,6 @@
       <c r="F260" t="n">
         <v>80</v>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7479,11 +6179,6 @@
       <c r="F261" t="n">
         <v>57</v>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7506,11 +6201,6 @@
       <c r="F262" t="n">
         <v>69</v>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7533,11 +6223,6 @@
       <c r="F263" t="n">
         <v>60</v>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7560,11 +6245,6 @@
       <c r="F264" t="n">
         <v>72</v>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7587,11 +6267,6 @@
       <c r="F265" t="n">
         <v>56</v>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7614,11 +6289,6 @@
       <c r="F266" t="n">
         <v>57</v>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7641,11 +6311,6 @@
       <c r="F267" t="n">
         <v>63</v>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7668,11 +6333,6 @@
       <c r="F268" t="n">
         <v>59</v>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7695,11 +6355,6 @@
       <c r="F269" t="n">
         <v>47</v>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -7722,11 +6377,6 @@
       <c r="F270" t="n">
         <v>65</v>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -7749,11 +6399,6 @@
       <c r="F271" t="n">
         <v>69</v>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -7776,11 +6421,6 @@
       <c r="F272" t="n">
         <v>67</v>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7803,11 +6443,6 @@
       <c r="F273" t="n">
         <v>56</v>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7830,11 +6465,6 @@
       <c r="F274" t="n">
         <v>89</v>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>202510.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7857,11 +6487,6 @@
       <c r="F275" t="n">
         <v>51</v>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7884,11 +6509,6 @@
       <c r="F276" t="n">
         <v>69</v>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7911,11 +6531,6 @@
       <c r="F277" t="n">
         <v>64</v>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7938,11 +6553,6 @@
       <c r="F278" t="n">
         <v>71</v>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7965,11 +6575,6 @@
       <c r="F279" t="n">
         <v>53</v>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7992,11 +6597,6 @@
       <c r="F280" t="n">
         <v>73</v>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8019,11 +6619,6 @@
       <c r="F281" t="n">
         <v>77</v>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8046,11 +6641,6 @@
       <c r="F282" t="n">
         <v>69</v>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8073,11 +6663,6 @@
       <c r="F283" t="n">
         <v>73</v>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8100,11 +6685,6 @@
       <c r="F284" t="n">
         <v>57</v>
       </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8127,11 +6707,6 @@
       <c r="F285" t="n">
         <v>55</v>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -8154,11 +6729,6 @@
       <c r="F286" t="n">
         <v>58</v>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -8181,11 +6751,6 @@
       <c r="F287" t="n">
         <v>57</v>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8208,11 +6773,6 @@
       <c r="F288" t="n">
         <v>72</v>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8235,11 +6795,6 @@
       <c r="F289" t="n">
         <v>88</v>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8262,11 +6817,6 @@
       <c r="F290" t="n">
         <v>63</v>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8289,11 +6839,6 @@
       <c r="F291" t="n">
         <v>61</v>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8316,11 +6861,6 @@
       <c r="F292" t="n">
         <v>53</v>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8343,11 +6883,6 @@
       <c r="F293" t="n">
         <v>60</v>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8370,11 +6905,6 @@
       <c r="F294" t="n">
         <v>58</v>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8397,11 +6927,6 @@
       <c r="F295" t="n">
         <v>72</v>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8424,11 +6949,6 @@
       <c r="F296" t="n">
         <v>52</v>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -8451,11 +6971,6 @@
       <c r="F297" t="n">
         <v>73</v>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -8478,11 +6993,6 @@
       <c r="F298" t="n">
         <v>51</v>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -8505,11 +7015,6 @@
       <c r="F299" t="n">
         <v>62</v>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -8532,11 +7037,6 @@
       <c r="F300" t="n">
         <v>56</v>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -8559,11 +7059,6 @@
       <c r="F301" t="n">
         <v>63</v>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -8586,11 +7081,6 @@
       <c r="F302" t="n">
         <v>70</v>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -8613,11 +7103,6 @@
       <c r="F303" t="n">
         <v>63</v>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -8640,11 +7125,6 @@
       <c r="F304" t="n">
         <v>63</v>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>202511.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -8667,11 +7147,6 @@
       <c r="F305" t="n">
         <v>40</v>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -8694,11 +7169,6 @@
       <c r="F306" t="n">
         <v>52</v>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -8721,11 +7191,6 @@
       <c r="F307" t="n">
         <v>49</v>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -8748,11 +7213,6 @@
       <c r="F308" t="n">
         <v>55</v>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -8775,11 +7235,6 @@
       <c r="F309" t="n">
         <v>50</v>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -8802,11 +7257,6 @@
       <c r="F310" t="n">
         <v>44</v>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -8829,11 +7279,6 @@
       <c r="F311" t="n">
         <v>49</v>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -8856,11 +7301,6 @@
       <c r="F312" t="n">
         <v>52</v>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -8883,11 +7323,6 @@
       <c r="F313" t="n">
         <v>55</v>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -8910,11 +7345,6 @@
       <c r="F314" t="n">
         <v>58</v>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -8937,11 +7367,6 @@
       <c r="F315" t="n">
         <v>0</v>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -8964,11 +7389,6 @@
       <c r="F316" t="n">
         <v>70</v>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -8991,11 +7411,6 @@
       <c r="F317" t="n">
         <v>31</v>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -9018,11 +7433,6 @@
       <c r="F318" t="n">
         <v>59</v>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -9045,11 +7455,6 @@
       <c r="F319" t="n">
         <v>60</v>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -9072,11 +7477,6 @@
       <c r="F320" t="n">
         <v>52</v>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -9099,11 +7499,6 @@
       <c r="F321" t="n">
         <v>53</v>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -9126,11 +7521,6 @@
       <c r="F322" t="n">
         <v>32</v>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -9153,11 +7543,6 @@
       <c r="F323" t="n">
         <v>60</v>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -9180,11 +7565,6 @@
       <c r="F324" t="n">
         <v>44</v>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -9207,11 +7587,6 @@
       <c r="F325" t="n">
         <v>0</v>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -9234,11 +7609,6 @@
       <c r="F326" t="n">
         <v>49</v>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -9261,11 +7631,6 @@
       <c r="F327" t="n">
         <v>55</v>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -9288,11 +7653,6 @@
       <c r="F328" t="n">
         <v>76</v>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -9315,11 +7675,6 @@
       <c r="F329" t="n">
         <v>0</v>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -9342,11 +7697,6 @@
       <c r="F330" t="n">
         <v>37</v>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -9369,11 +7719,6 @@
       <c r="F331" t="n">
         <v>54</v>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -9396,11 +7741,6 @@
       <c r="F332" t="n">
         <v>58</v>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -9423,11 +7763,6 @@
       <c r="F333" t="n">
         <v>59</v>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -9450,11 +7785,6 @@
       <c r="F334" t="n">
         <v>68</v>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -9477,11 +7807,6 @@
       <c r="F335" t="n">
         <v>77</v>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>202512.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -9504,11 +7829,6 @@
       <c r="F336" t="n">
         <v>62</v>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -9531,11 +7851,6 @@
       <c r="F337" t="n">
         <v>68</v>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -9558,11 +7873,6 @@
       <c r="F338" t="n">
         <v>59</v>
       </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -9585,11 +7895,6 @@
       <c r="F339" t="n">
         <v>48</v>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -9612,11 +7917,6 @@
       <c r="F340" t="n">
         <v>53</v>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -9639,11 +7939,6 @@
       <c r="F341" t="n">
         <v>54</v>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -9666,11 +7961,6 @@
       <c r="F342" t="n">
         <v>58</v>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -9693,11 +7983,6 @@
       <c r="F343" t="n">
         <v>61</v>
       </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -9720,11 +8005,6 @@
       <c r="F344" t="n">
         <v>64</v>
       </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -9747,11 +8027,6 @@
       <c r="F345" t="n">
         <v>57</v>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -9774,11 +8049,6 @@
       <c r="F346" t="n">
         <v>50</v>
       </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -9801,11 +8071,6 @@
       <c r="F347" t="n">
         <v>54</v>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -9828,11 +8093,6 @@
       <c r="F348" t="n">
         <v>0</v>
       </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -9855,11 +8115,6 @@
       <c r="F349" t="n">
         <v>62</v>
       </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -9882,11 +8137,6 @@
       <c r="F350" t="n">
         <v>58</v>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -9909,11 +8159,6 @@
       <c r="F351" t="n">
         <v>53</v>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -9936,11 +8181,6 @@
       <c r="F352" t="n">
         <v>65</v>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -9963,11 +8203,6 @@
       <c r="F353" t="n">
         <v>52</v>
       </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -9990,11 +8225,6 @@
       <c r="F354" t="n">
         <v>61</v>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -10017,11 +8247,6 @@
       <c r="F355" t="n">
         <v>52</v>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -10044,11 +8269,6 @@
       <c r="F356" t="n">
         <v>60</v>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -10071,11 +8291,6 @@
       <c r="F357" t="n">
         <v>54</v>
       </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -10098,11 +8313,6 @@
       <c r="F358" t="n">
         <v>51</v>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -10125,11 +8335,6 @@
       <c r="F359" t="n">
         <v>42</v>
       </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -10152,11 +8357,6 @@
       <c r="F360" t="n">
         <v>43</v>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -10179,11 +8379,6 @@
       <c r="F361" t="n">
         <v>59</v>
       </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -10206,11 +8401,6 @@
       <c r="F362" t="n">
         <v>41</v>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -10233,11 +8423,6 @@
       <c r="F363" t="n">
         <v>59</v>
       </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -10260,11 +8445,6 @@
       <c r="F364" t="n">
         <v>59</v>
       </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -10287,11 +8467,6 @@
       <c r="F365" t="n">
         <v>69</v>
       </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -10313,11 +8488,6 @@
       </c>
       <c r="F366" t="n">
         <v>56</v>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>202601.xlsx</t>
-        </is>
       </c>
     </row>
   </sheetData>
